--- a/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25914683583987</v>
+        <v>1.270927808290832</v>
       </c>
       <c r="C3" t="n">
-        <v>4.646726639741712</v>
+        <v>4.633531950596635</v>
       </c>
       <c r="D3" t="n">
-        <v>6.036634191408203</v>
+        <v>6.174275219543605</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94250766698979</v>
+        <v>12.07873497843107</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.384968856248771</v>
+        <v>1.43188285882408</v>
       </c>
       <c r="C4" t="n">
-        <v>5.177581159142359</v>
+        <v>5.135400816335892</v>
       </c>
       <c r="D4" t="n">
-        <v>6.388847081115033</v>
+        <v>6.509137879649955</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95139709650616</v>
+        <v>13.07642155480993</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.551486513782987</v>
+        <v>1.6519768824566</v>
       </c>
       <c r="C5" t="n">
-        <v>5.881550033053089</v>
+        <v>5.769968040341567</v>
       </c>
       <c r="D5" t="n">
-        <v>6.745961268420367</v>
+        <v>6.842544811626831</v>
       </c>
       <c r="E5" t="n">
-        <v>14.17899781525644</v>
+        <v>14.264489734425</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.737270031319899</v>
+        <v>1.901622139606269</v>
       </c>
       <c r="C6" t="n">
-        <v>6.733221606557884</v>
+        <v>6.534691471747561</v>
       </c>
       <c r="D6" t="n">
-        <v>7.081112712231452</v>
+        <v>7.259066186752094</v>
       </c>
       <c r="E6" t="n">
-        <v>15.55160435010924</v>
+        <v>15.69537979810593</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.945127921346307</v>
+        <v>2.188319717894378</v>
       </c>
       <c r="C7" t="n">
-        <v>7.742940418351774</v>
+        <v>7.428931163588203</v>
       </c>
       <c r="D7" t="n">
-        <v>7.453356913276521</v>
+        <v>7.707624047934782</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1414252529746</v>
+        <v>17.32487492941736</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.154924604230848</v>
+        <v>1.389881025163715</v>
       </c>
       <c r="C8" t="n">
-        <v>5.390626581366281</v>
+        <v>5.080238680599698</v>
       </c>
       <c r="D8" t="n">
-        <v>5.734759282730045</v>
+        <v>5.968047476802759</v>
       </c>
       <c r="E8" t="n">
-        <v>12.28031046832717</v>
+        <v>12.43816718256617</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.421838804883153</v>
+        <v>1.758371032433903</v>
       </c>
       <c r="C9" t="n">
-        <v>6.62814955549124</v>
+        <v>6.233450972159068</v>
       </c>
       <c r="D9" t="n">
-        <v>6.204404801223259</v>
+        <v>6.536860588429128</v>
       </c>
       <c r="E9" t="n">
-        <v>14.25439316159765</v>
+        <v>14.5286825930221</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.704148863440932</v>
+        <v>2.146950114734958</v>
       </c>
       <c r="C10" t="n">
-        <v>8.044863283906302</v>
+        <v>7.567557801438225</v>
       </c>
       <c r="D10" t="n">
-        <v>6.705119908872438</v>
+        <v>7.066732631363564</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45413205621967</v>
+        <v>16.78124054753675</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.9983513841755</v>
+        <v>2.539858839491334</v>
       </c>
       <c r="C11" t="n">
-        <v>9.564188162497805</v>
+        <v>9.010362630759534</v>
       </c>
       <c r="D11" t="n">
-        <v>7.197844305499288</v>
+        <v>7.563942898497343</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76038385217259</v>
+        <v>19.11416436874821</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.28527559813051</v>
+        <v>2.930632566498789</v>
       </c>
       <c r="C12" t="n">
-        <v>11.16861517703056</v>
+        <v>10.48107657168776</v>
       </c>
       <c r="D12" t="n">
-        <v>7.766485025003429</v>
+        <v>8.027714208503765</v>
       </c>
       <c r="E12" t="n">
-        <v>21.2203758001645</v>
+        <v>21.43942334669031</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.569093871548711</v>
+        <v>3.303349513300679</v>
       </c>
       <c r="C13" t="n">
-        <v>12.78433403429815</v>
+        <v>11.9644164386896</v>
       </c>
       <c r="D13" t="n">
-        <v>8.231185704666947</v>
+        <v>8.503751578240689</v>
       </c>
       <c r="E13" t="n">
-        <v>23.58461361051381</v>
+        <v>23.77151753023097</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.493532782470673</v>
+        <v>1.897109628732452</v>
       </c>
       <c r="C14" t="n">
-        <v>8.95552219309349</v>
+        <v>8.332534552409591</v>
       </c>
       <c r="D14" t="n">
-        <v>6.236542473750821</v>
+        <v>6.39652807963488</v>
       </c>
       <c r="E14" t="n">
-        <v>16.68559744931498</v>
+        <v>16.62617226077692</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.520707558924224</v>
+        <v>1.953020160489307</v>
       </c>
       <c r="C15" t="n">
-        <v>9.640526836254658</v>
+        <v>8.925068379307753</v>
       </c>
       <c r="D15" t="n">
-        <v>6.264404473597345</v>
+        <v>6.389341686439795</v>
       </c>
       <c r="E15" t="n">
-        <v>17.42563886877623</v>
+        <v>17.26743022623685</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.753175597812827</v>
+        <v>2.281954728797201</v>
       </c>
       <c r="C16" t="n">
-        <v>11.38049792744537</v>
+        <v>10.42277358952147</v>
       </c>
       <c r="D16" t="n">
-        <v>6.706426559957428</v>
+        <v>6.802078238782195</v>
       </c>
       <c r="E16" t="n">
-        <v>19.84010008521562</v>
+        <v>19.50680655710087</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.402082983820082</v>
+        <v>1.844134522611294</v>
       </c>
       <c r="C17" t="n">
-        <v>10.45405207137878</v>
+        <v>9.498517030835359</v>
       </c>
       <c r="D17" t="n">
-        <v>6.22019637447511</v>
+        <v>6.27882634737273</v>
       </c>
       <c r="E17" t="n">
-        <v>18.07633142967397</v>
+        <v>17.62147790081938</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.587564577583432</v>
+        <v>2.131207368810104</v>
       </c>
       <c r="C18" t="n">
-        <v>12.19070485532913</v>
+        <v>10.98701344758324</v>
       </c>
       <c r="D18" t="n">
-        <v>6.633541610394144</v>
+        <v>6.690846223891032</v>
       </c>
       <c r="E18" t="n">
-        <v>20.41181104330671</v>
+        <v>19.80906704028438</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.582587116722901</v>
+        <v>2.167846193132595</v>
       </c>
       <c r="C19" t="n">
-        <v>13.04674958352418</v>
+        <v>11.69230099831415</v>
       </c>
       <c r="D19" t="n">
-        <v>6.723253715608219</v>
+        <v>6.779164247365076</v>
       </c>
       <c r="E19" t="n">
-        <v>21.3525904158553</v>
+        <v>20.63931143881182</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.763827560403904</v>
+        <v>2.443255876604952</v>
       </c>
       <c r="C20" t="n">
-        <v>15.05383459008636</v>
+        <v>13.40360505654085</v>
       </c>
       <c r="D20" t="n">
-        <v>7.153475194563256</v>
+        <v>7.176104479146146</v>
       </c>
       <c r="E20" t="n">
-        <v>23.97113734505352</v>
+        <v>23.02296541229195</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.04861454038306</v>
+        <v>1.470363536650448</v>
       </c>
       <c r="C21" t="n">
-        <v>11.12294623471326</v>
+        <v>9.829258014919066</v>
       </c>
       <c r="D21" t="n">
-        <v>5.964028946005991</v>
+        <v>5.951639289978397</v>
       </c>
       <c r="E21" t="n">
-        <v>18.13558972110231</v>
+        <v>17.25126084154791</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270927808290832</v>
+        <v>1.255671448966837</v>
       </c>
       <c r="C3" t="n">
-        <v>4.633531950596635</v>
+        <v>4.599956179111394</v>
       </c>
       <c r="D3" t="n">
-        <v>6.174275219543605</v>
+        <v>6.060618287822954</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07873497843107</v>
+        <v>11.91624591590118</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.43188285882408</v>
+        <v>1.384305785907967</v>
       </c>
       <c r="C4" t="n">
-        <v>5.135400816335892</v>
+        <v>5.046924375802393</v>
       </c>
       <c r="D4" t="n">
-        <v>6.509137879649955</v>
+        <v>6.296435701255231</v>
       </c>
       <c r="E4" t="n">
-        <v>13.07642155480993</v>
+        <v>12.72766586296559</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.6519768824566</v>
+        <v>1.55438138608648</v>
       </c>
       <c r="C5" t="n">
-        <v>5.769968040341567</v>
+        <v>5.592191338606649</v>
       </c>
       <c r="D5" t="n">
-        <v>6.842544811626831</v>
+        <v>6.595921013295112</v>
       </c>
       <c r="E5" t="n">
-        <v>14.264489734425</v>
+        <v>13.74249373798824</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.901622139606269</v>
+        <v>1.757464763683466</v>
       </c>
       <c r="C6" t="n">
-        <v>6.534691471747561</v>
+        <v>6.253672343187244</v>
       </c>
       <c r="D6" t="n">
-        <v>7.259066186752094</v>
+        <v>7.01098892002832</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69537979810593</v>
+        <v>15.02212602689903</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.188319717894378</v>
+        <v>1.987951430936571</v>
       </c>
       <c r="C7" t="n">
-        <v>7.428931163588203</v>
+        <v>7.025139539884624</v>
       </c>
       <c r="D7" t="n">
-        <v>7.707624047934782</v>
+        <v>7.455265635610409</v>
       </c>
       <c r="E7" t="n">
-        <v>17.32487492941736</v>
+        <v>16.46835660643161</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.389881025163715</v>
+        <v>1.230354669892833</v>
       </c>
       <c r="C8" t="n">
-        <v>5.080238680599698</v>
+        <v>4.672093411087149</v>
       </c>
       <c r="D8" t="n">
-        <v>5.968047476802759</v>
+        <v>5.76190842889962</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43816718256617</v>
+        <v>11.6643565098796</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.758371032433903</v>
+        <v>1.564509731981794</v>
       </c>
       <c r="C9" t="n">
-        <v>6.233450972159068</v>
+        <v>5.693080668203278</v>
       </c>
       <c r="D9" t="n">
-        <v>6.536860588429128</v>
+        <v>6.285277128025839</v>
       </c>
       <c r="E9" t="n">
-        <v>14.5286825930221</v>
+        <v>13.54286752821091</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.146950114734958</v>
+        <v>1.920634874967647</v>
       </c>
       <c r="C10" t="n">
-        <v>7.567557801438225</v>
+        <v>6.883060590786892</v>
       </c>
       <c r="D10" t="n">
-        <v>7.066732631363564</v>
+        <v>6.878558956184464</v>
       </c>
       <c r="E10" t="n">
-        <v>16.78124054753675</v>
+        <v>15.682254421939</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.539858839491334</v>
+        <v>2.2846789321741</v>
       </c>
       <c r="C11" t="n">
-        <v>9.010362630759534</v>
+        <v>8.215201598625969</v>
       </c>
       <c r="D11" t="n">
-        <v>7.563942898497343</v>
+        <v>7.433505676945856</v>
       </c>
       <c r="E11" t="n">
-        <v>19.11416436874821</v>
+        <v>17.93338620774593</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.930632566498789</v>
+        <v>2.649182653897011</v>
       </c>
       <c r="C12" t="n">
-        <v>10.48107657168776</v>
+        <v>9.683409127316361</v>
       </c>
       <c r="D12" t="n">
-        <v>8.027714208503765</v>
+        <v>7.973420191973229</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43942334669031</v>
+        <v>20.3060119731866</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.303349513300679</v>
+        <v>3.003898599886329</v>
       </c>
       <c r="C13" t="n">
-        <v>11.9644164386896</v>
+        <v>11.27446509030844</v>
       </c>
       <c r="D13" t="n">
-        <v>8.503751578240689</v>
+        <v>8.516162591118279</v>
       </c>
       <c r="E13" t="n">
-        <v>23.77151753023097</v>
+        <v>22.79452628131305</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.897109628732452</v>
+        <v>1.72900496933427</v>
       </c>
       <c r="C14" t="n">
-        <v>8.332534552409591</v>
+        <v>7.992702584584556</v>
       </c>
       <c r="D14" t="n">
-        <v>6.39652807963488</v>
+        <v>6.47978028495501</v>
       </c>
       <c r="E14" t="n">
-        <v>16.62617226077692</v>
+        <v>16.20148783887383</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.953020160489307</v>
+        <v>1.780320921835251</v>
       </c>
       <c r="C15" t="n">
-        <v>8.925068379307753</v>
+        <v>8.786759762733462</v>
       </c>
       <c r="D15" t="n">
-        <v>6.389341686439795</v>
+        <v>6.541532215552134</v>
       </c>
       <c r="E15" t="n">
-        <v>17.26743022623685</v>
+        <v>17.10861290012085</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.281954728797201</v>
+        <v>2.084976869417121</v>
       </c>
       <c r="C16" t="n">
-        <v>10.42277358952147</v>
+        <v>10.59718106918092</v>
       </c>
       <c r="D16" t="n">
-        <v>6.802078238782195</v>
+        <v>7.039101587018505</v>
       </c>
       <c r="E16" t="n">
-        <v>19.50680655710087</v>
+        <v>19.72125952561655</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.844134522611294</v>
+        <v>1.686740730666445</v>
       </c>
       <c r="C17" t="n">
-        <v>9.498517030835359</v>
+        <v>10.02634386654661</v>
       </c>
       <c r="D17" t="n">
-        <v>6.27882634737273</v>
+        <v>6.548227734895097</v>
       </c>
       <c r="E17" t="n">
-        <v>17.62147790081938</v>
+        <v>18.26131233210815</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.131207368810104</v>
+        <v>1.930803209942202</v>
       </c>
       <c r="C18" t="n">
-        <v>10.98701344758324</v>
+        <v>11.87443483240602</v>
       </c>
       <c r="D18" t="n">
-        <v>6.690846223891032</v>
+        <v>7.011494841575082</v>
       </c>
       <c r="E18" t="n">
-        <v>19.80906704028438</v>
+        <v>20.8167328839233</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.167846193132595</v>
+        <v>1.937950333229119</v>
       </c>
       <c r="C19" t="n">
-        <v>11.69230099831415</v>
+        <v>12.87518917220705</v>
       </c>
       <c r="D19" t="n">
-        <v>6.779164247365076</v>
+        <v>7.118809683126303</v>
       </c>
       <c r="E19" t="n">
-        <v>20.63931143881182</v>
+        <v>21.93194918856247</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.443255876604952</v>
+        <v>2.164321718874348</v>
       </c>
       <c r="C20" t="n">
-        <v>13.40360505654085</v>
+        <v>14.91423988401951</v>
       </c>
       <c r="D20" t="n">
-        <v>7.176104479146146</v>
+        <v>7.654107618866876</v>
       </c>
       <c r="E20" t="n">
-        <v>23.02296541229195</v>
+        <v>24.73266922176073</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.470363536650448</v>
+        <v>1.289329259987336</v>
       </c>
       <c r="C21" t="n">
-        <v>9.829258014919066</v>
+        <v>11.04375846488871</v>
       </c>
       <c r="D21" t="n">
-        <v>5.951639289978397</v>
+        <v>6.400729959809057</v>
       </c>
       <c r="E21" t="n">
-        <v>17.25126084154791</v>
+        <v>18.7338176846851</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_44_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255671448966837</v>
+        <v>2.600825905020094</v>
       </c>
       <c r="C3" t="n">
-        <v>4.599956179111394</v>
+        <v>7.681829343391311</v>
       </c>
       <c r="D3" t="n">
-        <v>6.060618287822954</v>
+        <v>8.147021311272535</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91624591590118</v>
+        <v>18.42967655968394</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.384305785907967</v>
+        <v>1.094567919870243</v>
       </c>
       <c r="C4" t="n">
-        <v>5.046924375802393</v>
+        <v>4.4119247718244</v>
       </c>
       <c r="D4" t="n">
-        <v>6.296435701255231</v>
+        <v>5.682601654901829</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72766586296559</v>
+        <v>11.18909434659647</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.55438138608648</v>
+        <v>1.212133944196774</v>
       </c>
       <c r="C5" t="n">
-        <v>5.592191338606649</v>
+        <v>4.929841114520849</v>
       </c>
       <c r="D5" t="n">
-        <v>6.595921013295112</v>
+        <v>5.90399155080462</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74249373798824</v>
+        <v>12.04596660952224</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.757464763683466</v>
+        <v>1.348437903653779</v>
       </c>
       <c r="C6" t="n">
-        <v>6.253672343187244</v>
+        <v>5.608851302962785</v>
       </c>
       <c r="D6" t="n">
-        <v>7.01098892002832</v>
+        <v>6.20262269296805</v>
       </c>
       <c r="E6" t="n">
-        <v>15.02212602689903</v>
+        <v>13.15991189958461</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.987951430936571</v>
+        <v>1.498413277504499</v>
       </c>
       <c r="C7" t="n">
-        <v>7.025139539884624</v>
+        <v>6.44105383978195</v>
       </c>
       <c r="D7" t="n">
-        <v>7.455265635610409</v>
+        <v>6.610520397953342</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46835660643161</v>
+        <v>14.54998751523979</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.230354669892833</v>
+        <v>1.655626041245454</v>
       </c>
       <c r="C8" t="n">
-        <v>4.672093411087149</v>
+        <v>7.425763872707427</v>
       </c>
       <c r="D8" t="n">
-        <v>5.76190842889962</v>
+        <v>6.953669125626592</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6643565098796</v>
+        <v>16.03505903957947</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.564509731981794</v>
+        <v>1.814050745399007</v>
       </c>
       <c r="C9" t="n">
-        <v>5.693080668203278</v>
+        <v>8.607116895727088</v>
       </c>
       <c r="D9" t="n">
-        <v>6.285277128025839</v>
+        <v>7.377267926221002</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54286752821091</v>
+        <v>17.7984355673471</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.920634874967647</v>
+        <v>1.126133339110389</v>
       </c>
       <c r="C10" t="n">
-        <v>6.883060590786892</v>
+        <v>6.518068445420636</v>
       </c>
       <c r="D10" t="n">
-        <v>6.878558956184464</v>
+        <v>5.831797347720987</v>
       </c>
       <c r="E10" t="n">
-        <v>15.682254421939</v>
+        <v>13.47599913225201</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.2846789321741</v>
+        <v>1.07255936688964</v>
       </c>
       <c r="C11" t="n">
-        <v>8.215201598625969</v>
+        <v>6.974374960877511</v>
       </c>
       <c r="D11" t="n">
-        <v>7.433505676945856</v>
+        <v>5.68248333938209</v>
       </c>
       <c r="E11" t="n">
-        <v>17.93338620774593</v>
+        <v>13.72941766714924</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.649182653897011</v>
+        <v>1.173178689097896</v>
       </c>
       <c r="C12" t="n">
-        <v>9.683409127316361</v>
+        <v>8.320881207160182</v>
       </c>
       <c r="D12" t="n">
-        <v>7.973420191973229</v>
+        <v>6.108591295456334</v>
       </c>
       <c r="E12" t="n">
-        <v>20.3060119731866</v>
+        <v>15.60265119171441</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.003898599886329</v>
+        <v>0.936165158338631</v>
       </c>
       <c r="C13" t="n">
-        <v>11.27446509030844</v>
+        <v>8.012494618302174</v>
       </c>
       <c r="D13" t="n">
-        <v>8.516162591118279</v>
+        <v>5.582875217309209</v>
       </c>
       <c r="E13" t="n">
-        <v>22.79452628131305</v>
+        <v>14.53153499395001</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.72900496933427</v>
+        <v>1.031600852668463</v>
       </c>
       <c r="C14" t="n">
-        <v>7.992702584584556</v>
+        <v>9.491252097823931</v>
       </c>
       <c r="D14" t="n">
-        <v>6.47978028495501</v>
+        <v>5.985853197471397</v>
       </c>
       <c r="E14" t="n">
-        <v>16.20148783887383</v>
+        <v>16.50870614796379</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.780320921835251</v>
+        <v>1.011789183996763</v>
       </c>
       <c r="C15" t="n">
-        <v>8.786759762733462</v>
+        <v>10.36016753842166</v>
       </c>
       <c r="D15" t="n">
-        <v>6.541532215552134</v>
+        <v>6.058865774236233</v>
       </c>
       <c r="E15" t="n">
-        <v>17.10861290012085</v>
+        <v>17.43082249665465</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.084976869417121</v>
+        <v>1.114558533677319</v>
       </c>
       <c r="C16" t="n">
-        <v>10.59718106918092</v>
+        <v>12.16239125153865</v>
       </c>
       <c r="D16" t="n">
-        <v>7.039101587018505</v>
+        <v>6.447539690347545</v>
       </c>
       <c r="E16" t="n">
-        <v>19.72125952561655</v>
+        <v>19.72448947556352</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.686740730666445</v>
+        <v>0.6721928356207486</v>
       </c>
       <c r="C17" t="n">
-        <v>10.02634386654661</v>
+        <v>9.168365095374197</v>
       </c>
       <c r="D17" t="n">
-        <v>6.548227734895097</v>
+        <v>5.370061767459629</v>
       </c>
       <c r="E17" t="n">
-        <v>18.26131233210815</v>
+        <v>15.21061969845458</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.930803209942202</v>
+        <v>0.5322054304721959</v>
       </c>
       <c r="C18" t="n">
-        <v>11.87443483240602</v>
+        <v>8.221008013207154</v>
       </c>
       <c r="D18" t="n">
-        <v>7.011494841575082</v>
+        <v>4.89930392579624</v>
       </c>
       <c r="E18" t="n">
-        <v>20.8167328839233</v>
+        <v>13.65251736947559</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.937950333229119</v>
+        <v>0.6258837964114266</v>
       </c>
       <c r="C19" t="n">
-        <v>12.87518917220705</v>
+        <v>10.17953577831728</v>
       </c>
       <c r="D19" t="n">
-        <v>7.118809683126303</v>
+        <v>5.371230047227682</v>
       </c>
       <c r="E19" t="n">
-        <v>21.93194918856247</v>
+        <v>16.17664962195639</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.164321718874348</v>
+        <v>0.7133673343368599</v>
       </c>
       <c r="C20" t="n">
-        <v>14.91423988401951</v>
+        <v>12.21156699404438</v>
       </c>
       <c r="D20" t="n">
-        <v>7.654107618866876</v>
+        <v>5.858530337707628</v>
       </c>
       <c r="E20" t="n">
-        <v>24.73266922176073</v>
+        <v>18.78346466608886</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.289329259987336</v>
+        <v>0.7926238265007047</v>
       </c>
       <c r="C21" t="n">
-        <v>11.04375846488871</v>
+        <v>14.25941416528688</v>
       </c>
       <c r="D21" t="n">
-        <v>6.400729959809057</v>
+        <v>6.350837541479234</v>
       </c>
       <c r="E21" t="n">
-        <v>18.7338176846851</v>
+        <v>21.40287553326682</v>
       </c>
     </row>
   </sheetData>
